--- a/claude-with-tools/plots/c++_cost.xlsx
+++ b/claude-with-tools/plots/c++_cost.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/emmayu/Desktop/llm-with-tools/claude-with-tools/plots/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{238BE5B1-1E12-7A44-A7B8-5744B4D8EEF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76D4FF2E-F28E-034C-9EF1-33FB6B592FE5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1500" yWindow="1320" windowWidth="27640" windowHeight="16940" activeTab="4" xr2:uid="{22944BEF-51ED-8D4F-A900-C13B44E5FE01}"/>
   </bookViews>
@@ -469,10 +469,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.40914824999999999</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.33066424999999999</v>
       </c>
     </row>
   </sheetData>
@@ -502,10 +508,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.73938624999999902</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.29687825000000001</v>
       </c>
     </row>
   </sheetData>
@@ -535,10 +547,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.25861374999999998</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.157111</v>
       </c>
     </row>
   </sheetData>
@@ -568,10 +586,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.19669375</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.17390900000000001</v>
       </c>
     </row>
   </sheetData>
@@ -601,10 +625,16 @@
       <c r="A5" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B5">
+        <v>0.59343950000000001</v>
+      </c>
     </row>
     <row r="6" spans="1:2" ht="29">
       <c r="A6" s="1" t="s">
         <v>3</v>
+      </c>
+      <c r="B6">
+        <v>0.49073624999999899</v>
       </c>
     </row>
   </sheetData>
